--- a/job_application_forms/045_water_engineer_job_application_form--job_application_forms.xlsx
+++ b/job_application_forms/045_water_engineer_job_application_form--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'senior_water_engineer',_'label':_'senior_water_engineer'}</t>
+          <t>senior_water_engineer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'senior_water_engineer', 'label': 'Senior Water Engineer'}</t>
+          <t>Senior Water Engineer</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'water_engineer',_'label':_'water_engineer'}</t>
+          <t>water_engineer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'water_engineer', 'label': 'Water Engineer'}</t>
+          <t>Water Engineer</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active',_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'active', 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'inactive',_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'inactive', 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'full_time',_'label':_'full_time'}</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'full_time', 'label': 'Full Time'}</t>
+          <t>Full Time</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'part_time',_'label':_'part_time'}</t>
+          <t>part_time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'part_time', 'label': 'Part Time'}</t>
+          <t>Part Time</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'up_to_20_000',_'label':_'up_to_$20,000'}</t>
+          <t>up_to_$20,000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'up_to_20_000', 'label': 'Up to $20,000'}</t>
+          <t>Up to $20,000</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'20_000_to_40_000',_'label':_'$20,000_to_$40,000'}</t>
+          <t>$20,000_to_$40,000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '20_000_to_40_000', 'label': '$20,000 to $40,000'}</t>
+          <t>$20,000 to $40,000</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'40_000_to_60_000',_'label':_'$40,000_to_$60,000'}</t>
+          <t>$40,000_to_$60,000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '40_000_to_60_000', 'label': '$40,000 to $60,000'}</t>
+          <t>$40,000 to $60,000</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'60_000_to_80_000',_'label':_'$60,000_to_$80,000'}</t>
+          <t>$60,000_to_$80,000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': '60_000_to_80_000', 'label': '$60,000 to $80,000'}</t>
+          <t>$60,000 to $80,000</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'over_80_000',_'label':_'over_$80,000'}</t>
+          <t>over_$80,000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'over_80_000', 'label': 'Over $80,000'}</t>
+          <t>Over $80,000</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'contract',_'label':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'contract', 'label': 'Contract'}</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'permanent',_'label':_'permanent'}</t>
+          <t>permanent</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'permanent', 'label': 'Permanent'}</t>
+          <t>Permanent</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'water_engineering',_'label':_'water_engineering'}</t>
+          <t>water_engineering</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'water_engineering', 'label': 'Water Engineering'}</t>
+          <t>Water Engineering</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'environmental_engineering',_'label':_'environmental_engineering'}</t>
+          <t>environmental_engineering</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'environmental_engineering', 'label': 'Environmental Engineering'}</t>
+          <t>Environmental Engineering</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'junior',_'label':_'junior'}</t>
+          <t>junior</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'junior', 'label': 'Junior'}</t>
+          <t>Junior</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'senior',_'label':_'senior'}</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'senior', 'label': 'Senior'}</t>
+          <t>Senior</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'beginner',_'label':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'beginner', 'label': 'Beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'intermediate',_'label':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'intermediate', 'label': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'advanced',_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'advanced', 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
